--- a/Debt_Repayment_Plan-23.xlsx
+++ b/Debt_Repayment_Plan-23.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
   <si>
     <t>Month</t>
   </si>
@@ -162,21 +162,6 @@
   </si>
   <si>
     <t>Month 43</t>
-  </si>
-  <si>
-    <t>Month 44</t>
-  </si>
-  <si>
-    <t>Month 45</t>
-  </si>
-  <si>
-    <t>Month 46</t>
-  </si>
-  <si>
-    <t>Month 47</t>
-  </si>
-  <si>
-    <t>Month 48</t>
   </si>
 </sst>
 </file>
@@ -221,7 +206,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:G49"/>
+  <dimension ref="A1:G44"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="9.85546875" customWidth="true" bestFit="true"/>
@@ -261,22 +246,22 @@
         <v>7</v>
       </c>
       <c r="B2" t="n" s="0">
-        <v>10335.0</v>
+        <v>19435.0</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>129665.0</v>
+        <v>120565.0</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>3665.0</v>
+        <v>1500.0</v>
       </c>
       <c r="E2" t="n" s="0">
         <v>2080.0</v>
       </c>
       <c r="F2" t="n" s="0">
-        <v>1585.0</v>
+        <v>-580.0</v>
       </c>
       <c r="G2" t="n" s="0">
-        <v>778415.0</v>
+        <v>780580.0</v>
       </c>
     </row>
     <row r="3">
@@ -284,22 +269,22 @@
         <v>8</v>
       </c>
       <c r="B3" t="n" s="0">
-        <v>10335.0</v>
+        <v>19435.0</v>
       </c>
       <c r="C3" t="n" s="0">
-        <v>119330.0</v>
+        <v>101130.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>3665.0</v>
+        <v>1500.0</v>
       </c>
       <c r="E3" t="n" s="0">
-        <v>2075.773333333333</v>
+        <v>2081.5466666666666</v>
       </c>
       <c r="F3" t="n" s="0">
-        <v>1589.226666666667</v>
+        <v>-581.5466666666666</v>
       </c>
       <c r="G3" t="n" s="0">
-        <v>776825.7733333333</v>
+        <v>781161.5466666666</v>
       </c>
     </row>
     <row r="4">
@@ -307,22 +292,22 @@
         <v>9</v>
       </c>
       <c r="B4" t="n" s="0">
-        <v>10335.0</v>
+        <v>19435.0</v>
       </c>
       <c r="C4" t="n" s="0">
-        <v>108995.0</v>
+        <v>81695.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>3665.0</v>
+        <v>1500.0</v>
       </c>
       <c r="E4" t="n" s="0">
-        <v>2071.5353955555556</v>
+        <v>2083.0974577777774</v>
       </c>
       <c r="F4" t="n" s="0">
-        <v>1593.4646044444444</v>
+        <v>-583.0974577777774</v>
       </c>
       <c r="G4" t="n" s="0">
-        <v>775232.3087288889</v>
+        <v>781744.6441244445</v>
       </c>
     </row>
     <row r="5">
@@ -330,22 +315,22 @@
         <v>10</v>
       </c>
       <c r="B5" t="n" s="0">
-        <v>10335.0</v>
+        <v>19435.0</v>
       </c>
       <c r="C5" t="n" s="0">
-        <v>98660.0</v>
+        <v>62260.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>3665.0</v>
+        <v>1500.0</v>
       </c>
       <c r="E5" t="n" s="0">
-        <v>2067.28615661037</v>
+        <v>2084.652384331852</v>
       </c>
       <c r="F5" t="n" s="0">
-        <v>1597.7138433896298</v>
+        <v>-584.6523843318519</v>
       </c>
       <c r="G5" t="n" s="0">
-        <v>773634.5948854992</v>
+        <v>782329.2965087763</v>
       </c>
     </row>
     <row r="6">
@@ -353,22 +338,22 @@
         <v>11</v>
       </c>
       <c r="B6" t="n" s="0">
-        <v>10335.0</v>
+        <v>19435.0</v>
       </c>
       <c r="C6" t="n" s="0">
-        <v>88325.0</v>
+        <v>42825.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>3665.0</v>
+        <v>1500.0</v>
       </c>
       <c r="E6" t="n" s="0">
-        <v>2063.025586361331</v>
+        <v>2086.2114573567364</v>
       </c>
       <c r="F6" t="n" s="0">
-        <v>1601.974413638669</v>
+        <v>-586.2114573567364</v>
       </c>
       <c r="G6" t="n" s="0">
-        <v>772032.6204718605</v>
+        <v>782915.507966133</v>
       </c>
     </row>
     <row r="7">
@@ -376,22 +361,22 @@
         <v>12</v>
       </c>
       <c r="B7" t="n" s="0">
-        <v>10335.0</v>
+        <v>19435.0</v>
       </c>
       <c r="C7" t="n" s="0">
-        <v>77990.0</v>
+        <v>23390.0</v>
       </c>
       <c r="D7" t="n" s="0">
-        <v>3665.0</v>
+        <v>1500.0</v>
       </c>
       <c r="E7" t="n" s="0">
-        <v>2058.7536545916278</v>
+        <v>2087.7746879096876</v>
       </c>
       <c r="F7" t="n" s="0">
-        <v>1606.2463454083722</v>
+        <v>-587.7746879096876</v>
       </c>
       <c r="G7" t="n" s="0">
-        <v>770426.3741264521</v>
+        <v>783503.2826540426</v>
       </c>
     </row>
     <row r="8">
@@ -399,22 +384,22 @@
         <v>13</v>
       </c>
       <c r="B8" t="n" s="0">
-        <v>10335.0</v>
+        <v>19435.0</v>
       </c>
       <c r="C8" t="n" s="0">
-        <v>67655.0</v>
+        <v>3955.0</v>
       </c>
       <c r="D8" t="n" s="0">
-        <v>3665.0</v>
+        <v>1500.0</v>
       </c>
       <c r="E8" t="n" s="0">
-        <v>2054.470331003872</v>
+        <v>2089.3420870774466</v>
       </c>
       <c r="F8" t="n" s="0">
-        <v>1610.5296689961278</v>
+        <v>-589.3420870774466</v>
       </c>
       <c r="G8" t="n" s="0">
-        <v>768815.844457456</v>
+        <v>784092.62474112</v>
       </c>
     </row>
     <row r="9">
@@ -422,22 +407,22 @@
         <v>14</v>
       </c>
       <c r="B9" t="n" s="0">
-        <v>10335.0</v>
+        <v>19435.0</v>
       </c>
       <c r="C9" t="n" s="0">
-        <v>57320.0</v>
+        <v>0.0</v>
       </c>
       <c r="D9" t="n" s="0">
-        <v>3665.0</v>
+        <v>23000.0</v>
       </c>
       <c r="E9" t="n" s="0">
-        <v>2050.1755852198826</v>
+        <v>2090.91366597632</v>
       </c>
       <c r="F9" t="n" s="0">
-        <v>1614.8244147801174</v>
+        <v>20909.08633402368</v>
       </c>
       <c r="G9" t="n" s="0">
-        <v>767201.0200426759</v>
+        <v>763183.5384070964</v>
       </c>
     </row>
     <row r="10">
@@ -445,22 +430,22 @@
         <v>15</v>
       </c>
       <c r="B10" t="n" s="0">
-        <v>10335.0</v>
+        <v>0.0</v>
       </c>
       <c r="C10" t="n" s="0">
-        <v>46985.0</v>
+        <v>0.0</v>
       </c>
       <c r="D10" t="n" s="0">
-        <v>3665.0</v>
+        <v>23000.0</v>
       </c>
       <c r="E10" t="n" s="0">
-        <v>2045.869386780469</v>
+        <v>2035.1561024189236</v>
       </c>
       <c r="F10" t="n" s="0">
-        <v>1619.130613219531</v>
+        <v>20964.843897581075</v>
       </c>
       <c r="G10" t="n" s="0">
-        <v>765581.8894294563</v>
+        <v>742218.6945095153</v>
       </c>
     </row>
     <row r="11">
@@ -468,22 +453,22 @@
         <v>16</v>
       </c>
       <c r="B11" t="n" s="0">
-        <v>10335.0</v>
+        <v>0.0</v>
       </c>
       <c r="C11" t="n" s="0">
-        <v>36650.0</v>
+        <v>0.0</v>
       </c>
       <c r="D11" t="n" s="0">
-        <v>3665.0</v>
+        <v>23000.0</v>
       </c>
       <c r="E11" t="n" s="0">
-        <v>2041.5517051452168</v>
+        <v>1979.2498520253741</v>
       </c>
       <c r="F11" t="n" s="0">
-        <v>1623.4482948547832</v>
+        <v>21020.750147974624</v>
       </c>
       <c r="G11" t="n" s="0">
-        <v>763958.4411346015</v>
+        <v>721197.9443615407</v>
       </c>
     </row>
     <row r="12">
@@ -491,22 +476,22 @@
         <v>17</v>
       </c>
       <c r="B12" t="n" s="0">
-        <v>10335.0</v>
+        <v>0.0</v>
       </c>
       <c r="C12" t="n" s="0">
-        <v>26315.0</v>
+        <v>0.0</v>
       </c>
       <c r="D12" t="n" s="0">
-        <v>3665.0</v>
+        <v>23000.0</v>
       </c>
       <c r="E12" t="n" s="0">
-        <v>2037.2225096922705</v>
+        <v>1923.1945182974418</v>
       </c>
       <c r="F12" t="n" s="0">
-        <v>1627.7774903077295</v>
+        <v>21076.80548170256</v>
       </c>
       <c r="G12" t="n" s="0">
-        <v>762330.6636442938</v>
+        <v>700121.1388798382</v>
       </c>
     </row>
     <row r="13">
@@ -514,22 +499,22 @@
         <v>18</v>
       </c>
       <c r="B13" t="n" s="0">
-        <v>10335.0</v>
+        <v>0.0</v>
       </c>
       <c r="C13" t="n" s="0">
-        <v>15980.0</v>
+        <v>0.0</v>
       </c>
       <c r="D13" t="n" s="0">
-        <v>3665.0</v>
+        <v>23000.0</v>
       </c>
       <c r="E13" t="n" s="0">
-        <v>2032.8817697181166</v>
+        <v>1866.9897036795685</v>
       </c>
       <c r="F13" t="n" s="0">
-        <v>1632.1182302818834</v>
+        <v>21133.01029632043</v>
       </c>
       <c r="G13" t="n" s="0">
-        <v>760698.5454140119</v>
+        <v>678988.1285835177</v>
       </c>
     </row>
     <row r="14">
@@ -537,22 +522,22 @@
         <v>19</v>
       </c>
       <c r="B14" t="n" s="0">
-        <v>10335.0</v>
+        <v>0.0</v>
       </c>
       <c r="C14" t="n" s="0">
-        <v>5645.0</v>
+        <v>0.0</v>
       </c>
       <c r="D14" t="n" s="0">
-        <v>3665.0</v>
+        <v>23000.0</v>
       </c>
       <c r="E14" t="n" s="0">
-        <v>2028.529454437365</v>
+        <v>1810.6350095560472</v>
       </c>
       <c r="F14" t="n" s="0">
-        <v>1636.470545562635</v>
+        <v>21189.36499044395</v>
       </c>
       <c r="G14" t="n" s="0">
-        <v>759062.0748684492</v>
+        <v>657798.7635930738</v>
       </c>
     </row>
     <row r="15">
@@ -560,7 +545,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n" s="0">
-        <v>10335.0</v>
+        <v>0.0</v>
       </c>
       <c r="C15" t="n" s="0">
         <v>0.0</v>
@@ -569,13 +554,13 @@
         <v>23000.0</v>
       </c>
       <c r="E15" t="n" s="0">
-        <v>2024.1655329825312</v>
+        <v>1754.1300362481968</v>
       </c>
       <c r="F15" t="n" s="0">
-        <v>20975.83446701747</v>
+        <v>21245.869963751804</v>
       </c>
       <c r="G15" t="n" s="0">
-        <v>738086.2404014318</v>
+        <v>636552.8936293221</v>
       </c>
     </row>
     <row r="16">
@@ -592,13 +577,13 @@
         <v>23000.0</v>
       </c>
       <c r="E16" t="n" s="0">
-        <v>1968.229974403818</v>
+        <v>1697.4743830115253</v>
       </c>
       <c r="F16" t="n" s="0">
-        <v>21031.770025596183</v>
+        <v>21302.525616988474</v>
       </c>
       <c r="G16" t="n" s="0">
-        <v>717054.4703758357</v>
+        <v>615250.3680123336</v>
       </c>
     </row>
     <row r="17">
@@ -615,13 +600,13 @@
         <v>23000.0</v>
       </c>
       <c r="E17" t="n" s="0">
-        <v>1912.1452543355617</v>
+        <v>1640.6676480328897</v>
       </c>
       <c r="F17" t="n" s="0">
-        <v>21087.854745664437</v>
+        <v>21359.33235196711</v>
       </c>
       <c r="G17" t="n" s="0">
-        <v>695966.6156301713</v>
+        <v>593891.0356603665</v>
       </c>
     </row>
     <row r="18">
@@ -638,13 +623,13 @@
         <v>23000.0</v>
       </c>
       <c r="E18" t="n" s="0">
-        <v>1855.91097501379</v>
+        <v>1583.709428427644</v>
       </c>
       <c r="F18" t="n" s="0">
-        <v>21144.08902498621</v>
+        <v>21416.290571572357</v>
       </c>
       <c r="G18" t="n" s="0">
-        <v>674822.526605185</v>
+        <v>572474.7450887942</v>
       </c>
     </row>
     <row r="19">
@@ -661,13 +646,13 @@
         <v>23000.0</v>
       </c>
       <c r="E19" t="n" s="0">
-        <v>1799.5267376138265</v>
+        <v>1526.5993202367843</v>
       </c>
       <c r="F19" t="n" s="0">
-        <v>21200.473262386175</v>
+        <v>21473.400679763217</v>
       </c>
       <c r="G19" t="n" s="0">
-        <v>653622.0533427988</v>
+        <v>551001.344409031</v>
       </c>
     </row>
     <row r="20">
@@ -684,13 +669,13 @@
         <v>23000.0</v>
       </c>
       <c r="E20" t="n" s="0">
-        <v>1742.9921422474636</v>
+        <v>1469.3369184240826</v>
       </c>
       <c r="F20" t="n" s="0">
-        <v>21257.007857752535</v>
+        <v>21530.663081575916</v>
       </c>
       <c r="G20" t="n" s="0">
-        <v>632365.0454850463</v>
+        <v>529470.6813274551</v>
       </c>
     </row>
     <row r="21">
@@ -707,13 +692,13 @@
         <v>23000.0</v>
       </c>
       <c r="E21" t="n" s="0">
-        <v>1686.3067879601235</v>
+        <v>1411.9218168732136</v>
       </c>
       <c r="F21" t="n" s="0">
-        <v>21313.693212039878</v>
+        <v>21588.078183126785</v>
       </c>
       <c r="G21" t="n" s="0">
-        <v>611051.3522730065</v>
+        <v>507882.6031443283</v>
       </c>
     </row>
     <row r="22">
@@ -730,13 +715,13 @@
         <v>23000.0</v>
       </c>
       <c r="E22" t="n" s="0">
-        <v>1629.470272728017</v>
+        <v>1354.3536083848753</v>
       </c>
       <c r="F22" t="n" s="0">
-        <v>21370.529727271984</v>
+        <v>21645.646391615126</v>
       </c>
       <c r="G22" t="n" s="0">
-        <v>589680.8225457345</v>
+        <v>486236.9567527132</v>
       </c>
     </row>
     <row r="23">
@@ -753,13 +738,13 @@
         <v>23000.0</v>
       </c>
       <c r="E23" t="n" s="0">
-        <v>1572.482193455292</v>
+        <v>1296.6318846739018</v>
       </c>
       <c r="F23" t="n" s="0">
-        <v>21427.517806544707</v>
+        <v>21703.3681153261</v>
       </c>
       <c r="G23" t="n" s="0">
-        <v>568253.3047391898</v>
+        <v>464533.5886373871</v>
       </c>
     </row>
     <row r="24">
@@ -776,13 +761,13 @@
         <v>23000.0</v>
       </c>
       <c r="E24" t="n" s="0">
-        <v>1515.3421459711728</v>
+        <v>1238.7562363663656</v>
       </c>
       <c r="F24" t="n" s="0">
-        <v>21484.65785402883</v>
+        <v>21761.243763633633</v>
       </c>
       <c r="G24" t="n" s="0">
-        <v>546768.6468851609</v>
+        <v>442772.34487375343</v>
       </c>
     </row>
     <row r="25">
@@ -799,13 +784,13 @@
         <v>23000.0</v>
       </c>
       <c r="E25" t="n" s="0">
-        <v>1458.0497250270957</v>
+        <v>1180.7262529966758</v>
       </c>
       <c r="F25" t="n" s="0">
-        <v>21541.950274972904</v>
+        <v>21819.273747003324</v>
       </c>
       <c r="G25" t="n" s="0">
-        <v>525226.696610188</v>
+        <v>420953.0711267501</v>
       </c>
     </row>
     <row r="26">
@@ -822,13 +807,13 @@
         <v>23000.0</v>
       </c>
       <c r="E26" t="n" s="0">
-        <v>1400.6045242938346</v>
+        <v>1122.541523004667</v>
       </c>
       <c r="F26" t="n" s="0">
-        <v>21599.395475706166</v>
+        <v>21877.458476995333</v>
       </c>
       <c r="G26" t="n" s="0">
-        <v>503627.30113448185</v>
+        <v>399075.61264975474</v>
       </c>
     </row>
     <row r="27">
@@ -845,13 +830,13 @@
         <v>23000.0</v>
       </c>
       <c r="E27" t="n" s="0">
-        <v>1343.0061363586183</v>
+        <v>1064.2016337326793</v>
       </c>
       <c r="F27" t="n" s="0">
-        <v>21656.993863641383</v>
+        <v>21935.79836626732</v>
       </c>
       <c r="G27" t="n" s="0">
-        <v>481970.30727084045</v>
+        <v>377139.8142834874</v>
       </c>
     </row>
     <row r="28">
@@ -868,13 +853,13 @@
         <v>23000.0</v>
       </c>
       <c r="E28" t="n" s="0">
-        <v>1285.254152722241</v>
+        <v>1005.706171422633</v>
       </c>
       <c r="F28" t="n" s="0">
-        <v>21714.745847277758</v>
+        <v>21994.293828577367</v>
       </c>
       <c r="G28" t="n" s="0">
-        <v>460255.5614235627</v>
+        <v>355145.52045491</v>
       </c>
     </row>
     <row r="29">
@@ -891,13 +876,13 @@
         <v>23000.0</v>
       </c>
       <c r="E29" t="n" s="0">
-        <v>1227.3481637961672</v>
+        <v>947.0547212130933</v>
       </c>
       <c r="F29" t="n" s="0">
-        <v>21772.651836203833</v>
+        <v>22052.945278786905</v>
       </c>
       <c r="G29" t="n" s="0">
-        <v>438482.9095873589</v>
+        <v>333092.5751761231</v>
       </c>
     </row>
     <row r="30">
@@ -914,13 +899,13 @@
         <v>23000.0</v>
       </c>
       <c r="E30" t="n" s="0">
-        <v>1169.2877588996237</v>
+        <v>888.2468671363283</v>
       </c>
       <c r="F30" t="n" s="0">
-        <v>21830.712241100377</v>
+        <v>22111.753132863672</v>
       </c>
       <c r="G30" t="n" s="0">
-        <v>416652.1973462585</v>
+        <v>310980.82204325945</v>
       </c>
     </row>
     <row r="31">
@@ -937,13 +922,13 @@
         <v>23000.0</v>
       </c>
       <c r="E31" t="n" s="0">
-        <v>1111.0725262566893</v>
+        <v>829.2821921153585</v>
       </c>
       <c r="F31" t="n" s="0">
-        <v>21888.92747374331</v>
+        <v>22170.71780788464</v>
       </c>
       <c r="G31" t="n" s="0">
-        <v>394763.2698725152</v>
+        <v>288810.10423537483</v>
       </c>
     </row>
     <row r="32">
@@ -960,13 +945,13 @@
         <v>23000.0</v>
       </c>
       <c r="E32" t="n" s="0">
-        <v>1052.7020529933739</v>
+        <v>770.1602779609996</v>
       </c>
       <c r="F32" t="n" s="0">
-        <v>21947.297947006628</v>
+        <v>22229.839722039</v>
       </c>
       <c r="G32" t="n" s="0">
-        <v>372815.9719255085</v>
+        <v>266580.26451333583</v>
       </c>
     </row>
     <row r="33">
@@ -983,13 +968,13 @@
         <v>23000.0</v>
       </c>
       <c r="E33" t="n" s="0">
-        <v>994.1759251346894</v>
+        <v>710.8807053688955</v>
       </c>
       <c r="F33" t="n" s="0">
-        <v>22005.82407486531</v>
+        <v>22289.119294631106</v>
       </c>
       <c r="G33" t="n" s="0">
-        <v>350810.1478506432</v>
+        <v>244291.1452187047</v>
       </c>
     </row>
     <row r="34">
@@ -1006,13 +991,13 @@
         <v>23000.0</v>
       </c>
       <c r="E34" t="n" s="0">
-        <v>935.4937276017151</v>
+        <v>651.4430539165459</v>
       </c>
       <c r="F34" t="n" s="0">
-        <v>22064.506272398285</v>
+        <v>22348.556946083456</v>
       </c>
       <c r="G34" t="n" s="0">
-        <v>328745.6415782449</v>
+        <v>221942.58827262124</v>
       </c>
     </row>
     <row r="35">
@@ -1029,13 +1014,13 @@
         <v>23000.0</v>
       </c>
       <c r="E35" t="n" s="0">
-        <v>876.6550442086531</v>
+        <v>591.8469020603233</v>
       </c>
       <c r="F35" t="n" s="0">
-        <v>22123.34495579135</v>
+        <v>22408.153097939678</v>
       </c>
       <c r="G35" t="n" s="0">
-        <v>306622.29662245355</v>
+        <v>199534.43517468157</v>
       </c>
     </row>
     <row r="36">
@@ -1052,13 +1037,13 @@
         <v>23000.0</v>
       </c>
       <c r="E36" t="n" s="0">
-        <v>817.6594576598761</v>
+        <v>532.0918271324841</v>
       </c>
       <c r="F36" t="n" s="0">
-        <v>22182.340542340124</v>
+        <v>22467.908172867516</v>
       </c>
       <c r="G36" t="n" s="0">
-        <v>284439.9560801134</v>
+        <v>177066.52700181404</v>
       </c>
     </row>
     <row r="37">
@@ -1075,13 +1060,13 @@
         <v>23000.0</v>
       </c>
       <c r="E37" t="n" s="0">
-        <v>758.5065495469692</v>
+        <v>472.1774053381708</v>
       </c>
       <c r="F37" t="n" s="0">
-        <v>22241.493450453032</v>
+        <v>22527.82259466183</v>
       </c>
       <c r="G37" t="n" s="0">
-        <v>262198.4626296604</v>
+        <v>154538.70440715223</v>
       </c>
     </row>
     <row r="38">
@@ -1098,13 +1083,13 @@
         <v>23000.0</v>
       </c>
       <c r="E38" t="n" s="0">
-        <v>699.195900345761</v>
+        <v>412.1032117524059</v>
       </c>
       <c r="F38" t="n" s="0">
-        <v>22300.80409965424</v>
+        <v>22587.896788247595</v>
       </c>
       <c r="G38" t="n" s="0">
-        <v>239897.65853000613</v>
+        <v>131950.80761890463</v>
       </c>
     </row>
     <row r="39">
@@ -1121,13 +1106,13 @@
         <v>23000.0</v>
       </c>
       <c r="E39" t="n" s="0">
-        <v>639.7270894133496</v>
+        <v>351.868820317079</v>
       </c>
       <c r="F39" t="n" s="0">
-        <v>22360.27291058665</v>
+        <v>22648.13117968292</v>
       </c>
       <c r="G39" t="n" s="0">
-        <v>217537.38561941948</v>
+        <v>109302.6764392217</v>
       </c>
     </row>
     <row r="40">
@@ -1144,13 +1129,13 @@
         <v>23000.0</v>
       </c>
       <c r="E40" t="n" s="0">
-        <v>580.0996949851186</v>
+        <v>291.47380383792455</v>
       </c>
       <c r="F40" t="n" s="0">
-        <v>22419.900305014882</v>
+        <v>22708.526196162074</v>
       </c>
       <c r="G40" t="n" s="0">
-        <v>195117.4853144046</v>
+        <v>86594.15024305963</v>
       </c>
     </row>
     <row r="41">
@@ -1167,13 +1152,13 @@
         <v>23000.0</v>
       </c>
       <c r="E41" t="n" s="0">
-        <v>520.3132941717456</v>
+        <v>230.91773398149235</v>
       </c>
       <c r="F41" t="n" s="0">
-        <v>22479.686705828255</v>
+        <v>22769.082266018508</v>
       </c>
       <c r="G41" t="n" s="0">
-        <v>172637.79860857633</v>
+        <v>63825.06797704112</v>
       </c>
     </row>
     <row r="42">
@@ -1190,13 +1175,13 @@
         <v>23000.0</v>
       </c>
       <c r="E42" t="n" s="0">
-        <v>460.3674629562035</v>
+        <v>170.20018127210966</v>
       </c>
       <c r="F42" t="n" s="0">
-        <v>22539.632537043795</v>
+        <v>22829.79981872789</v>
       </c>
       <c r="G42" t="n" s="0">
-        <v>150098.16607153253</v>
+        <v>40995.268158313236</v>
       </c>
     </row>
     <row r="43">
@@ -1213,13 +1198,13 @@
         <v>23000.0</v>
       </c>
       <c r="E43" t="n" s="0">
-        <v>400.2617761907534</v>
+        <v>109.3207150888353</v>
       </c>
       <c r="F43" t="n" s="0">
-        <v>22599.738223809247</v>
+        <v>22890.679284911166</v>
       </c>
       <c r="G43" t="n" s="0">
-        <v>127498.42784772327</v>
+        <v>18104.58887340207</v>
       </c>
     </row>
     <row r="44">
@@ -1236,127 +1221,12 @@
         <v>23000.0</v>
       </c>
       <c r="E44" t="n" s="0">
-        <v>339.9958075939287</v>
+        <v>48.27890366240552</v>
       </c>
       <c r="F44" t="n" s="0">
-        <v>22660.00419240607</v>
+        <v>18104.58887340207</v>
       </c>
       <c r="G44" t="n" s="0">
-        <v>104838.4236553172</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="s" s="0">
-        <v>50</v>
-      </c>
-      <c r="B45" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="C45" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="D45" t="n" s="0">
-        <v>23000.0</v>
-      </c>
-      <c r="E45" t="n" s="0">
-        <v>279.56912974751253</v>
-      </c>
-      <c r="F45" t="n" s="0">
-        <v>22720.430870252487</v>
-      </c>
-      <c r="G45" t="n" s="0">
-        <v>82117.99278506471</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="s" s="0">
-        <v>51</v>
-      </c>
-      <c r="B46" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="C46" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="D46" t="n" s="0">
-        <v>23000.0</v>
-      </c>
-      <c r="E46" t="n" s="0">
-        <v>218.9813140935059</v>
-      </c>
-      <c r="F46" t="n" s="0">
-        <v>22781.018685906492</v>
-      </c>
-      <c r="G46" t="n" s="0">
-        <v>59336.974099158215</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="s" s="0">
-        <v>52</v>
-      </c>
-      <c r="B47" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="C47" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="D47" t="n" s="0">
-        <v>23000.0</v>
-      </c>
-      <c r="E47" t="n" s="0">
-        <v>158.23193093108856</v>
-      </c>
-      <c r="F47" t="n" s="0">
-        <v>22841.768069068912</v>
-      </c>
-      <c r="G47" t="n" s="0">
-        <v>36495.206030089306</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="s" s="0">
-        <v>53</v>
-      </c>
-      <c r="B48" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="C48" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="D48" t="n" s="0">
-        <v>23000.0</v>
-      </c>
-      <c r="E48" t="n" s="0">
-        <v>97.32054941357148</v>
-      </c>
-      <c r="F48" t="n" s="0">
-        <v>22902.679450586427</v>
-      </c>
-      <c r="G48" t="n" s="0">
-        <v>13592.526579502879</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="s" s="0">
-        <v>54</v>
-      </c>
-      <c r="B49" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="C49" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="D49" t="n" s="0">
-        <v>23000.0</v>
-      </c>
-      <c r="E49" t="n" s="0">
-        <v>36.24673754534101</v>
-      </c>
-      <c r="F49" t="n" s="0">
-        <v>13592.526579502879</v>
-      </c>
-      <c r="G49" t="n" s="0">
         <v>0.0</v>
       </c>
     </row>
